--- a/dados/excel/genero_gap_salarial.xlsx
+++ b/dados/excel/genero_gap_salarial.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -894,63 +894,63 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>AUX. DE FISCALIZACAO</t>
+          <t>MEDICO 75H</t>
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>7542.0805</v>
+        <v>18156.35356741573</v>
       </c>
       <c r="C2" s="10" t="n">
-        <v>0</v>
+        <v>21927.08078947368</v>
       </c>
       <c r="D2" s="9" t="n">
-        <v>10249.05746575342</v>
+        <v>23881.19489361702</v>
       </c>
       <c r="E2" s="9" t="n">
-        <v>11</v>
+        <v>134</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G2" s="9" t="n">
-        <v>17</v>
+        <v>157</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>2706.98</v>
+        <v>5724.84</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>26.41</v>
+        <v>23.97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>MEDICO 75H</t>
+          <t>AUX. DE FISCALIZACAO</t>
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>18119.00360410095</v>
+        <v>8103.940909090909</v>
       </c>
       <c r="C3" s="14" t="n">
-        <v>22169.60281690141</v>
+        <v>0</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>23956.7898799435</v>
+        <v>10482.53320987654</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>134</v>
+        <v>11</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G3" s="13" t="n">
-        <v>157</v>
+        <v>17</v>
       </c>
       <c r="H3" s="15" t="n">
-        <v>5837.79</v>
+        <v>2378.59</v>
       </c>
       <c r="I3" s="13" t="n">
-        <v>24.37</v>
+        <v>22.69</v>
       </c>
     </row>
     <row r="4">
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>6307.0065</v>
+        <v>6331.037777777778</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>0</v>
+        <v>4119.37</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>8281.37654605263</v>
+        <v>8130.915377906977</v>
       </c>
       <c r="E4" s="9" t="n">
         <v>10</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>1974.37</v>
+        <v>1799.88</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>23.84</v>
+        <v>22.14</v>
       </c>
     </row>
     <row r="5">
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>14156.64812854442</v>
+        <v>14299.75212765958</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>13953.95714285714</v>
+        <v>13905.7275</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>17617.14863636364</v>
+        <v>17819.38492021277</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>82</v>
@@ -1009,10 +1009,10 @@
         <v>47</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>3460.5</v>
+        <v>3519.63</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>19.64</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="6">
@@ -1022,16 +1022,16 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>21935.22129629629</v>
+        <v>21729.88428571428</v>
       </c>
       <c r="C6" s="10" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>26735.40878453039</v>
+        <v>26182.44570731707</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -1040,41 +1040,41 @@
         <v>39</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>4800.19</v>
+        <v>4452.56</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>17.95</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>COORDENADOR ADMINISTRATIVO(FG)</t>
+          <t>CIRURGIAO DENTISTA 75H</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>15167.88173611111</v>
+        <v>17319.57536585366</v>
       </c>
       <c r="C7" s="14" t="n">
-        <v>13178.92</v>
+        <v>22533.06272727273</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>18335.99615384615</v>
+        <v>20573.55902272727</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F7" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>3168.11</v>
+        <v>3253.98</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>17.28</v>
+        <v>15.82</v>
       </c>
     </row>
     <row r="8">
@@ -1084,13 +1084,13 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>6308.689358600584</v>
+        <v>6461.886701570681</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>6275.59</v>
+        <v>6348.397</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>7615.326216216215</v>
+        <v>7588.658556149732</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>38</v>
@@ -1102,41 +1102,41 @@
         <v>39</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>1306.64</v>
+        <v>1126.77</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>17.16</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>CIRURGIAO DENTISTA 75H</t>
+          <t>COORDENADOR ADMINISTRATIVO(FG)</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>17151.39148514852</v>
+        <v>15444.267</v>
       </c>
       <c r="C9" s="14" t="n">
-        <v>22017.783</v>
+        <v>9743.593333333332</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>20517.62168831169</v>
+        <v>17995.86325842697</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F9" s="15" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>3366.23</v>
+        <v>2551.6</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>16.41</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="10">
@@ -1146,13 +1146,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>7007.386313253011</v>
+        <v>6982.888615702479</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>7047.258823529412</v>
+        <v>7745.81157894737</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>8040.133134564644</v>
+        <v>8002.224890210429</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>68</v>
@@ -1164,10 +1164,10 @@
         <v>294</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>1032.75</v>
+        <v>1019.34</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>12.84</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="11">
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>5308.317331111784</v>
+        <v>5382.467752655953</v>
       </c>
       <c r="C11" s="14" t="n">
-        <v>6927.426097560975</v>
+        <v>7016.67409090909</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>6077.041524440762</v>
+        <v>6155.426046511628</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>360</v>
@@ -1195,10 +1195,10 @@
         <v>138</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>768.72</v>
+        <v>772.96</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>12.65</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="12">
@@ -1208,28 +1208,28 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>14688.2073258532</v>
+        <v>14787.75215621105</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>12890.72421052632</v>
+        <v>13169.33714285714</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>16701.87663082437</v>
+        <v>16698.0221086262</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="F12" s="11" t="n">
         <v>2</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>2013.67</v>
+        <v>1910.27</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>12.06</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="13">
@@ -1239,13 +1239,13 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>20453.08273809524</v>
+        <v>20732.77357894737</v>
       </c>
       <c r="C13" s="14" t="n">
         <v>13286.156</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>23060.5388034188</v>
+        <v>23342.56175572519</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>15</v>
@@ -1257,72 +1257,72 @@
         <v>16</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>2607.46</v>
+        <v>2609.79</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>11.31</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>MEDICO II 150H</t>
+          <t>PEB I CLT</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>18780.61933333333</v>
+        <v>6503.948242147923</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>0</v>
+        <v>6924.54</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>20121.16578571429</v>
+        <v>7089.751495327103</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>12</v>
+        <v>571</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>1340.55</v>
+        <v>585.8</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>6.66</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>TEC.DE CONTROLE ADMINISTRATIVO</t>
+          <t>MEDICO II 150H</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>4831.560414078675</v>
+        <v>18800.45757281553</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>6986.849638554217</v>
+        <v>0</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>5135.0566741447</v>
+        <v>20043.66658227848</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>335</v>
+        <v>12</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>225</v>
+        <v>17</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>303.5</v>
+        <v>1243.21</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>5.91</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>968.1992452830189</v>
+        <v>964.4743859649122</v>
       </c>
       <c r="C16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1027.176842105263</v>
+        <v>1026.798181818182</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>31</v>
@@ -1350,41 +1350,41 @@
         <v>15</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>58.98</v>
+        <v>62.32</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>5.74</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>PEB I CLT</t>
+          <t>TEC.DE CONTROLE ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>6787.527385804638</v>
+        <v>4863.39057404022</v>
       </c>
       <c r="C17" s="14" t="n">
-        <v>6915.916086956522</v>
+        <v>7055.607391304348</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>7153.668181818182</v>
+        <v>5175.958175944334</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>547</v>
+        <v>337</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>19</v>
+        <v>227</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>366.14</v>
+        <v>312.57</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>5.12</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="18">
@@ -1394,16 +1394,16 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>11963.95114183765</v>
+        <v>12074.28337589784</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>10650.134</v>
+        <v>10885.30727272727</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>12574.91635416667</v>
+        <v>12849.87514285714</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F18" s="11" t="n">
         <v>1</v>
@@ -1412,103 +1412,103 @@
         <v>10</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>610.97</v>
+        <v>775.59</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>4.86</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>TECNICO DE ENFERMAGEM</t>
+          <t>AGENTE DE COMBATE AS ENDEMIAS</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>6857.964430120729</v>
+        <v>4711.739970845481</v>
       </c>
       <c r="C19" s="14" t="n">
-        <v>7338.392111111111</v>
+        <v>726.47</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>7184.1725</v>
+        <v>4906.384487632509</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>526</v>
+        <v>37</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>136</v>
+        <v>31</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>326.21</v>
+        <v>194.64</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>4.54</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>AGENTE DE COMBATE AS ENDEMIAS</t>
+          <t>TECNICO DE ENFERMAGEM</t>
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>4687.639278688524</v>
+        <v>6931.821465786094</v>
       </c>
       <c r="C20" s="10" t="n">
-        <v>726.47</v>
+        <v>7432.587910447761</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>4886.26592</v>
+        <v>7208.516868402534</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>37</v>
+        <v>526</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>30</v>
+        <v>136</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>198.63</v>
+        <v>276.7</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>4.06</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>FISCAL DE SAUDE PUBLICA</t>
+          <t>ESTAGIARIO NIVEL SUPERIOR</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>6017.698299319728</v>
+        <v>994.5456962025316</v>
       </c>
       <c r="C21" s="14" t="n">
-        <v>0</v>
+        <v>897.2984615384615</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>6237.593779527559</v>
+        <v>1028.652635445363</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>18</v>
+        <v>717</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>16</v>
+        <v>204</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>219.9</v>
+        <v>34.11</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>3.53</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="22">
@@ -1518,13 +1518,13 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>3918.879136795904</v>
+        <v>4029.07940131579</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>3483.832580645161</v>
+        <v>3517.005142857143</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>4061.78329113924</v>
+        <v>4154.60873015873</v>
       </c>
       <c r="E22" s="9" t="n">
         <v>159</v>
@@ -1533,44 +1533,44 @@
         <v>4</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>142.9</v>
+        <v>125.53</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>3.52</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>AGENTE COMUNITARIO DE SAUDE</t>
+          <t>CIRURGIAO DENTISTA I 150H</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>4464.017660472973</v>
+        <v>18355.09246666667</v>
       </c>
       <c r="C23" s="14" t="n">
-        <v>5082.601875</v>
+        <v>0</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>4623.552680412371</v>
+        <v>18918.46007633588</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>159.54</v>
+        <v>563.37</v>
       </c>
       <c r="I23" s="13" t="n">
-        <v>3.45</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="24">
@@ -1580,152 +1580,152 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>14569.61957831325</v>
+        <v>14609.11808243728</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>15745.11</v>
+        <v>14468.67727272727</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>15089.03006944444</v>
+        <v>15033.96659021407</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>519.41</v>
+        <v>424.85</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>3.44</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>CIRURGIAO DENTISTA I 150H</t>
+          <t>FISCAL DE SAUDE PUBLICA</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>18239.0707518797</v>
+        <v>6077.411212121212</v>
       </c>
       <c r="C25" s="14" t="n">
         <v>0</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>18864.4788034188</v>
+        <v>6245.168680555556</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F25" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>625.41</v>
+        <v>167.76</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>3.32</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>ESTAGIARIO NIVEL SUPERIOR</t>
+          <t>CHEFE DE DIVISAO</t>
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>994.7710643274854</v>
+        <v>15033.59518904824</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>881.6733333333333</v>
+        <v>21322.36090909091</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>1028.150317948718</v>
+        <v>15400.71076388889</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>687</v>
+        <v>92</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>193</v>
+        <v>53</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>33.38</v>
+        <v>367.12</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>CHEFE DE DIVISAO</t>
+          <t>AGENTE COMUNITARIO DE SAUDE</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>14923.89472834068</v>
+        <v>4514.619379207181</v>
       </c>
       <c r="C27" s="14" t="n">
-        <v>20950.17947368421</v>
+        <v>5158.505555555555</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>15173.72205729167</v>
+        <v>4609.480438596492</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="F27" s="15" t="n">
         <v>2</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>249.83</v>
+        <v>94.86</v>
       </c>
       <c r="I27" s="13" t="n">
-        <v>1.65</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>GCM-CLASSE ESPECIAL</t>
+          <t>ENG.CIVIL I</t>
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>13734.84915492958</v>
+        <v>12117.03352331606</v>
       </c>
       <c r="C28" s="10" t="n">
-        <v>9287.174000000001</v>
+        <v>0</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>13815.69628378378</v>
+        <v>12202.03558951965</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>80.84999999999999</v>
+        <v>85</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="29">
@@ -1735,59 +1735,59 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>11251.96103797468</v>
+        <v>11384.01562782805</v>
       </c>
       <c r="C29" s="14" t="n">
-        <v>8644.0375</v>
+        <v>8733.377142857144</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>11315.57287047841</v>
+        <v>11402.04585161964</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>198</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="n">
         <v>111</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>63.61</v>
+        <v>18.03</v>
       </c>
       <c r="I29" s="13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>ENG.CIVIL I</t>
+          <t>PEBII ED.FISICA</t>
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>12041.97610465116</v>
+        <v>11021.70415730337</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>0</v>
+        <v>13201.338125</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>12043.08703614458</v>
+        <v>11010.9685882353</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>1.11</v>
+        <v>-10.74</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>0.01</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="31">
@@ -1797,16 +1797,16 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>10391.93738095238</v>
+        <v>10529.4730952381</v>
       </c>
       <c r="C31" s="14" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>10367.13074074074</v>
+        <v>10481.98141666667</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F31" s="15" t="n">
         <v>0</v>
@@ -1815,41 +1815,41 @@
         <v>23</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-24.81</v>
+        <v>-47.49</v>
       </c>
       <c r="I31" s="13" t="n">
-        <v>-0.24</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>PEBII ED.FISICA</t>
+          <t>GCM-CLASSE ESPECIAL</t>
         </is>
       </c>
       <c r="B32" s="9" t="n">
-        <v>10833.92425619835</v>
+        <v>13941.61448717949</v>
       </c>
       <c r="C32" s="10" t="n">
-        <v>12903.99448275862</v>
+        <v>9814.855000000001</v>
       </c>
       <c r="D32" s="9" t="n">
-        <v>10781.44052083333</v>
+        <v>13832.70057228916</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>-52.48</v>
+        <v>-108.91</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>-0.49</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="33">
@@ -1859,13 +1859,13 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1025.430188679245</v>
+        <v>1030.842821576764</v>
       </c>
       <c r="C33" s="14" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>1009.003218390805</v>
+        <v>1013.776470588235</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>44</v>
@@ -1874,13 +1874,13 @@
         <v>0</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>-16.43</v>
+        <v>-17.07</v>
       </c>
       <c r="I33" s="13" t="n">
-        <v>-1.63</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="34">
@@ -1890,28 +1890,28 @@
         </is>
       </c>
       <c r="B34" s="9" t="n">
-        <v>4331.192177462527</v>
+        <v>4420.368410067155</v>
       </c>
       <c r="C34" s="10" t="n">
-        <v>4188.360909090909</v>
+        <v>4275.333803418804</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>4253.131757215619</v>
+        <v>4345.757714723926</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>1592</v>
+        <v>1609</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>-78.06</v>
+        <v>-74.61</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>-1.84</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="35">
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>8629.999289940828</v>
+        <v>8656.491132743364</v>
       </c>
       <c r="C35" s="14" t="n">
-        <v>9476.893</v>
+        <v>9784.049090909091</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>8473.303142857143</v>
+        <v>8385.407070707071</v>
       </c>
       <c r="E35" s="13" t="n">
         <v>56</v>
@@ -1939,10 +1939,10 @@
         <v>20</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>-156.7</v>
+        <v>-271.08</v>
       </c>
       <c r="I35" s="13" t="n">
-        <v>-1.85</v>
+        <v>-3.23</v>
       </c>
     </row>
     <row r="36">
@@ -1952,13 +1952,13 @@
         </is>
       </c>
       <c r="B36" s="9" t="n">
-        <v>13180.20008264463</v>
+        <v>13313.58318181818</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>8416.965625000001</v>
+        <v>8459.061176470588</v>
       </c>
       <c r="D36" s="9" t="n">
-        <v>12589.30849637681</v>
+        <v>12843.77755775577</v>
       </c>
       <c r="E36" s="9" t="n">
         <v>14</v>
@@ -1970,103 +1970,103 @@
         <v>131</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>-590.89</v>
+        <v>-469.81</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>-4.69</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>PEB I</t>
+          <t>CHEFE DE GABINETE</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>11111.05401191609</v>
+        <v>17859.43456140351</v>
       </c>
       <c r="C37" s="14" t="n">
-        <v>10438.75046153846</v>
+        <v>15422.22875</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>10569.05433470508</v>
+        <v>17053.08058252427</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>2117</v>
+        <v>14</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-542</v>
+        <v>-806.35</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>-5.13</v>
+        <v>-4.73</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>CHEFE DE GABINETE</t>
+          <t>PEB I</t>
         </is>
       </c>
       <c r="B38" s="9" t="n">
-        <v>18218.74666666667</v>
+        <v>11326.35278264024</v>
       </c>
       <c r="C38" s="10" t="n">
-        <v>15422.22875</v>
+        <v>10573.1725087108</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>17130.93319148936</v>
+        <v>10768.17515451174</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>14</v>
+        <v>2171</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>-1087.81</v>
+        <v>-558.1799999999999</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>-6.35</v>
+        <v>-5.18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>PROCURADOR</t>
+          <t>SECRETARIO DE ESCOLA</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>33909.79579617835</v>
+        <v>5433.158392857143</v>
       </c>
       <c r="C39" s="14" t="n">
-        <v>0</v>
+        <v>8251.130000000001</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>31814.10751824818</v>
+        <v>5049.654104477612</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-2095.69</v>
+        <v>-383.5</v>
       </c>
       <c r="I39" s="13" t="n">
-        <v>-6.59</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="40">
@@ -2076,59 +2076,59 @@
         </is>
       </c>
       <c r="B40" s="9" t="n">
-        <v>16178.45779483037</v>
+        <v>16360.60545586107</v>
       </c>
       <c r="C40" s="10" t="n">
         <v>0</v>
       </c>
       <c r="D40" s="9" t="n">
-        <v>15080.74503649635</v>
+        <v>15020.05404530744</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>-1097.71</v>
+        <v>-1340.55</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>-7.28</v>
+        <v>-8.93</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>SECRETARIO DE ESCOLA</t>
+          <t>PROCURADOR</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>5316.22656679151</v>
+        <v>34430.78182857143</v>
       </c>
       <c r="C41" s="14" t="n">
-        <v>8133.600833333333</v>
+        <v>0</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>4953.878691275168</v>
+        <v>31310.02961538462</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>-362.35</v>
+        <v>-3120.75</v>
       </c>
       <c r="I41" s="13" t="n">
-        <v>-7.31</v>
+        <v>-9.970000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -2138,28 +2138,28 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>1765.226566598484</v>
+        <v>1813.164491856169</v>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1824.782564102564</v>
+        <v>1854.588681318681</v>
       </c>
       <c r="D42" s="9" t="n">
-        <v>1442.819077490775</v>
+        <v>1493.283056443025</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>3329</v>
+        <v>3627</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>-322.41</v>
+        <v>-319.88</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>-22.35</v>
+        <v>-21.42</v>
       </c>
     </row>
     <row r="43">
@@ -2169,13 +2169,13 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>24115.68706896552</v>
+        <v>24359.10083969466</v>
       </c>
       <c r="C43" s="14" t="n">
-        <v>15740.47333333334</v>
+        <v>15878.47</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>17572.85193548387</v>
+        <v>17490.49276190476</v>
       </c>
       <c r="E43" s="13" t="n">
         <v>12</v>
@@ -2187,10 +2187,10 @@
         <v>10</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-6542.84</v>
+        <v>-6868.61</v>
       </c>
       <c r="I43" s="13" t="n">
-        <v>-37.23</v>
+        <v>-39.27</v>
       </c>
     </row>
   </sheetData>
